--- a/data/subaru_raw.xlsx
+++ b/data/subaru_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ottob\Documents\Projects\Data Analytics\ghg-emissions-benchmarking\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6807AB1-9153-43C5-9DAE-D5C8EE6AEA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156539C4-183F-454E-BE75-A09DFB501982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,16 +260,9 @@
     <t>Report did not disclose any third-party assurance.</t>
   </si>
   <si>
-    <t>Restated — see Sustainability Website 2023, p.72: (1,726,493 t-CO₂). 
-See Sustainability Website 2024, p.46, fn.: "Retroactive correction has been made to data from previous years due to revisions to the calculation method-."</t>
-  </si>
-  <si>
     <t>Restated — see Sustainability Website 2024, p.46: (31,864,033 t-CO₂).</t>
   </si>
   <si>
-    <t>Not restated — see Integrated Report 2024, p.47.</t>
-  </si>
-  <si>
     <t>Not restated — see Integrated Report 2023, p.45.</t>
   </si>
   <si>
@@ -277,10 +270,6 @@
   </si>
   <si>
     <t>Consolidated number, inclusion of part-time employees not specified — see Integrated Report 2025, p.50.</t>
-  </si>
-  <si>
-    <t>Not restated — see Integrated Report 2024, p.47. 
-Consolidated number, inclusion of part-time employees not specified — see Integrated Report 2025, p.50.</t>
   </si>
   <si>
     <t>Not restated — see Integrated Report 2023, p.45. 
@@ -291,26 +280,6 @@
   </si>
   <si>
     <t>Subaru</t>
-  </si>
-  <si>
-    <t>Subaru states this figure is market-based, using emission factors from each electricity utility (Japan: Ministry of the Environment list; U.S.: Edison Electric Institute and U.S. EPA; Canada: government values) — see Sustainability Website 2025, p.52.</t>
-  </si>
-  <si>
-    <t>Subaru states its Scope 2 figure is market-based, using emission factors from each electricity utility (Japan: Ministry of the Environment list; U.S.: Edison Electric Institute and U.S. EPA; Canada: government values) — see Sustainability Website 2025, p.52.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WORKBOOK: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>v1.0, 2026-10-16</t>
-    </r>
   </si>
   <si>
     <r>
@@ -695,32 +664,66 @@
 The stated scope of domestic Group companies also changed from 52 consolidated subsidiaries (including 33 dealerships) to 39 (including 23) — see Sustainability Website 2024, p.51, and 2025, p.52.</t>
   </si>
   <si>
+    <t>Restated — see Sustainability Website 2023, p.72: (1,726,493 t-CO₂). 
+See Sustainability Website 2024, p.46, fn: “Retroactive correction has been made to data from previous years due to revisions to the calculation method for “1 Purchased goods and services” and “12 End-of-life treatment of sold products.””</t>
+  </si>
+  <si>
+    <t>Restated — see Sustainability Website 2024, p.46: (577,694 t-CO₂). 
+See Sustainability Website 2025, p.54, fn: “Retroactive correction has been made to data from previous years due to revisions to the calculation method for “12 End-of-life treatment of sold products” and “13 Leased assets (downstream)””</t>
+  </si>
+  <si>
+    <t>Restated — see Sustainability Website 2023, p.72: (480,917 t-CO₂). 
+See Sustainability Website 2025, p.54, fn: “Retroactive correction has been made to data from previous years due to revisions to the calculation method for “12 End-of-life treatment of sold products” and “13 Leased assets (downstream)””</t>
+  </si>
+  <si>
+    <t>Restated — see Sustainability Website 2024, p.46: (1,562 t-CO₂). 
+See Sustainability Website 2025, p.54, fn: “Retroactive correction has been made to data from previous years due to revisions to the calculation method for “12 End-of-life treatment of sold products” and “13 Leased assets (downstream)””</t>
+  </si>
+  <si>
+    <t>Restated — see Sustainability Website 2023, p.72: (1,984 t-CO₂). 
+See Sustainability Website 2025, p.54, fn: “Retroactive correction has been made to data from previous years due to revisions to the calculation method for “12 End-of-life treatment of sold products” and “13 Leased assets (downstream)””</t>
+  </si>
+  <si>
+    <t>Subaru does not label its Scope 2 figure as market- or location-based; it lists emission-factor sources for both methods — see Sustainability Website 2025, p.52. 
+This project uses it as the company’s Scope 2 figure.</t>
+  </si>
+  <si>
     <t>Restated — see Sustainability Website 2024, p.51: (207,966 t-CO₂). 
-Subaru states this figure is market-based, using emission factors from each electricity utility (Japan: Ministry of the Environment list; U.S.: Edison Electric Institute and U.S. EPA; Canada: government values) — see Sustainability Website 2025, p.52. 
+Subaru does not label its Scope 2 figure as market- or location-based; it lists emission-factor sources for both methods — see Sustainability Website 2025, p.52. 
+This project uses it as the company’s Scope 2 figure. 
 Subaru states errors were found in aggregated data and prior years were corrected — see Sustainability Website 2025, p.52. 
 The stated scope of domestic Group companies also changed from 52 consolidated subsidiaries (including 33 dealerships) to 39 (including 23) — see Sustainability Website 2024, p.51, and 2025, p.52.</t>
   </si>
   <si>
+    <t>Not disclosed. Subaru reports one Scope 2 figure without stating its basis, although it lists emission-factor sources for both market- and location-based methods — see Sustainability Website 2025, p.52.</t>
+  </si>
+  <si>
+    <t>Not restated — see Integrated Report 2024, p.47.</t>
+  </si>
+  <si>
+    <t>Not restated — see Integrated Report 2024, p.47. 
+Consolidated number, inclusion of part-time employees not specified — see Integrated Report 2025, p.50.</t>
+  </si>
+  <si>
     <t>Restated — see Sustainability Website 2023, p.71: (228,273 t-CO₂). 
-Subaru states this figure is market-based, using emission factors from each electricity utility (Japan: Ministry of the Environment list; U.S.: Edison Electric Institute and U.S. EPA; Canada: government values) — see Sustainability Website 2025, p.52.
+Subaru does not label its Scope 2 figure as market- or location-based; it lists emission-factor sources for both methods — see Sustainability Website 2025, p.52. 
+This project uses it as the company’s Scope 2 figure. 
 Subaru states errors were found in aggregated data and prior years were corrected — see Sustainability Website 2025, p.52. 
 The stated scope of domestic Group companies also changed from 52 consolidated subsidiaries (including 33 dealerships) to 39 (including 23) — see Sustainability Website 2024, p.51, and 2025, p.52.</t>
   </si>
   <si>
-    <t>Restated — see Sustainability Website 2024, p.46: (577,694 t-CO₂). 
-See Sustainability Website 2025, p.54, fn: "Retroactive correction has been made to data from previous years due to revisions to the calculation method-."</t>
-  </si>
-  <si>
-    <t>Restated — see Sustainability Website 2023, p.72: (480,917 t-CO₂). 
-See Sustainability Website 2025, p.54, fn: "Retroactive correction has been made to data from previous years due to revisions to the calculation method-."</t>
-  </si>
-  <si>
-    <t>Restated — see Sustainability Website 2024, p.46: (1,562 t-CO₂). 
-See Sustainability Website 2025, p.54, fn: "Retroactive correction has been made to data from previous years due to revisions to the calculation method-."</t>
-  </si>
-  <si>
-    <t>Restated — see Sustainability Website 2023, p.72: (1,984 t-CO₂). 
-See Sustainability Website 2025, p.54, fn: "Retroactive correction has been made to data from previous years due to revisions to the calculation method-."</t>
+    <r>
+      <t xml:space="preserve">WORKBOOK: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>v1.0, 2026-10-17</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1400,7 +1403,7 @@
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="10"/>
       <c r="B1" s="23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C1" s="23"/>
       <c r="D1" s="23"/>
@@ -1409,7 +1412,7 @@
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
       <c r="B2" s="24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
@@ -1418,7 +1421,7 @@
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="24" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
@@ -1427,7 +1430,7 @@
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -1450,7 +1453,7 @@
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="14" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1459,7 +1462,7 @@
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
@@ -1468,7 +1471,7 @@
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -1477,7 +1480,7 @@
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -1486,7 +1489,7 @@
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="21" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -1509,7 +1512,7 @@
     <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15"/>
       <c r="B14" s="17" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -1518,13 +1521,13 @@
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E15" s="15"/>
     </row>
@@ -1534,36 +1537,36 @@
         <v>62</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="15"/>
       <c r="B17" s="19" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="15"/>
       <c r="B18" s="19" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E18" s="15"/>
     </row>
@@ -1573,36 +1576,36 @@
         <v>61</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A20" s="15"/>
       <c r="B20" s="19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="15"/>
       <c r="B21" s="19" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E21" s="15"/>
     </row>
@@ -1623,7 +1626,7 @@
     <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15"/>
       <c r="B24" s="17" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -1632,7 +1635,7 @@
     <row r="25" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="15"/>
       <c r="B25" s="26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
@@ -1641,10 +1644,10 @@
     <row r="26" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="15"/>
       <c r="B26" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="15"/>
@@ -1652,7 +1655,7 @@
     <row r="27" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15"/>
       <c r="B27" s="20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -1793,7 +1796,7 @@
         <v>57</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>58</v>
@@ -1892,7 +1895,7 @@
         <v>50</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J2" s="4"/>
     </row>
@@ -1922,7 +1925,7 @@
         <v>50</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="J3" s="4"/>
     </row>
@@ -1952,7 +1955,7 @@
         <v>50</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -2010,7 +2013,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="J6" s="4"/>
     </row>
@@ -2040,7 +2043,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -2098,7 +2101,7 @@
         <v>50</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="J9" s="4"/>
     </row>
@@ -2128,7 +2131,7 @@
         <v>50</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -2140,7 +2143,7 @@
         <v>45747</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" s="7">
         <v>936</v>
@@ -2168,7 +2171,7 @@
         <v>45382</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D12" s="7">
         <v>976</v>
@@ -2186,7 +2189,7 @@
         <v>50</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="J12" s="4"/>
     </row>
@@ -2198,7 +2201,7 @@
         <v>45016</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D13" s="7">
         <v>852</v>
@@ -2216,7 +2219,7 @@
         <v>50</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J13" s="4"/>
     </row>
@@ -2266,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>5</v>
@@ -2353,7 +2356,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>71</v>
@@ -2392,14 +2395,14 @@
         <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>71</v>
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="78.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -2431,12 +2434,12 @@
         <v>26</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="78.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
@@ -2468,12 +2471,12 @@
         <v>26</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" ht="78.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
@@ -2505,7 +2508,7 @@
         <v>26</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -2542,7 +2545,7 @@
         <v>52</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>71</v>
@@ -2620,7 +2623,7 @@
         <v>52</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>71</v>
@@ -2824,7 +2827,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>5</v>
@@ -2924,7 +2927,7 @@
       </c>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="125" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
@@ -2959,7 +2962,7 @@
         <v>53</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>71</v>
@@ -4149,7 +4152,7 @@
         <v>53</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>71</v>
@@ -4238,7 +4241,7 @@
       </c>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" ht="125" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
         <v>57</v>
       </c>
@@ -4273,13 +4276,13 @@
         <v>53</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" ht="125" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
         <v>57</v>
       </c>
@@ -4314,7 +4317,7 @@
         <v>53</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>71</v>
@@ -4361,7 +4364,7 @@
       </c>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:14" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" ht="125" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
@@ -4396,14 +4399,14 @@
         <v>53</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>71</v>
       </c>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14" ht="94" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" ht="125" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
         <v>57</v>
       </c>
@@ -4438,7 +4441,7 @@
         <v>53</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>71</v>
